--- a/data/Daily_Out_Standing.xlsx
+++ b/data/Daily_Out_Standing.xlsx
@@ -2,25 +2,82 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\RECAPO\Code Base\NNF_Recapo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
     <sheet name="Collected" sheetId="2" r:id="rId2"/>
+    <sheet name="PIVOT" sheetId="3" r:id="rId3"/>
+    <sheet name="DASH" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlcn.WorksheetConnection_Daily_Out_Standing.xlsxTable11" hidden="1">Table1[]</definedName>
+    <definedName name="Slicer_Day">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="202" r:id="rId5"/>
+    <pivotCache cacheId="205" r:id="rId6"/>
+    <pivotCache cacheId="208" r:id="rId7"/>
+    <pivotCache cacheId="211" r:id="rId8"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
+      <x14:pivotCaches>
+        <pivotCache cacheId="201" r:id="rId9"/>
+      </x14:pivotCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId10"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
+      <x15:dataModel>
+        <x15:modelTables>
+          <x15:modelTable id="Table1" name="Table1" connection="WorksheetConnection_Daily_Out_Standing.xlsx!Table1"/>
+        </x15:modelTables>
+      </x15:dataModel>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="6" minRefreshableVersion="5" background="1">
+    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="" model="1"/>
+      </ext>
+    </extLst>
+  </connection>
+  <connection id="2" name="WorksheetConnection_Daily_Out_Standing.xlsx!Table1" type="102" refreshedVersion="6" minRefreshableVersion="5">
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="Table1" autoDelete="1">
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Daily_Out_Standing.xlsxTable11"/>
+        </x15:connection>
+      </ext>
+    </extLst>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>Db id</t>
   </si>
@@ -44,6 +101,24 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Outstanding</t>
+  </si>
+  <si>
+    <t>Sum of Difference_Outstanding</t>
+  </si>
+  <si>
+    <t>Difference_Rise</t>
+  </si>
+  <si>
+    <t>Sum of Difference_Rise</t>
   </si>
 </sst>
 </file>
@@ -536,7 +611,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,6 +631,18 @@
     <xf numFmtId="8" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -601,13 +688,16 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -618,7 +708,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -649,15 +739,7827 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable4</c:name>
+    <c:fmtId val="15"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$E$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$D$11:$D$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$E$11:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>683489</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>993143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E82C-4B79-BB38-6CA7BE73A62C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1601924495"/>
+        <c:axId val="1601921999"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1601924495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601921999"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1601921999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601924495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable3</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$B$11:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>683489</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>993143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FD9B-40FE-B222-4CAD0A2119E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="483106432"/>
+        <c:axId val="483104768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="483106432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483104768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="483104768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483106432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable1</c:name>
+    <c:fmtId val="20"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$A$21:$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$B$21:$B$25</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>180656</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>309654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8898-405C-8355-17B7DC39487A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="199646304"/>
+        <c:axId val="199652128"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="199646304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="199652128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="199652128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="199646304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable4</c:name>
+    <c:fmtId val="18"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1"/>
+              </a:gs>
+              <a:gs pos="75000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="51000">
+                <a:schemeClr val="accent1">
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                  <a:alpha val="15000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="10800000" scaled="1"/>
+            <a:tileRect/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.8538567334615528E-2"/>
+          <c:y val="7.496112281739431E-2"/>
+          <c:w val="0.80572649713149114"/>
+          <c:h val="0.76730324202432443"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$E$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="10800000" scaled="1"/>
+              <a:tileRect/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$D$11:$D$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$E$11:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>683489</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>993143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5558-411E-A426-E235EA0C9F7E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="326"/>
+        <c:overlap val="-58"/>
+        <c:axId val="1601924495"/>
+        <c:axId val="1601921999"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1601924495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601921999"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1601921999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601924495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable3</c:name>
+    <c:fmtId val="16"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{B8635B81-8830-4591-9F21-02E57C20B3FF}" type="VALUE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr sz="1500" baseline="0"/>
+                  </a:pPr>
+                  <a:t>[VALUE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="0"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B8635B81-8830-4591-9F21-02E57C20B3FF}" type="VALUE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[VALUE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$B$11:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>683489</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>993143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2818-46D2-BEDB-22055906BB39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="483106432"/>
+        <c:axId val="483104768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="483106432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483104768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="483104768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483106432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable1</c:name>
+    <c:fmtId val="23"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>DIffrence Rise</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:alpha val="84000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="228600">
+              <a:schemeClr val="accent1">
+                <a:satMod val="175000"/>
+                <a:alpha val="40000"/>
+              </a:schemeClr>
+            </a:glow>
+            <a:softEdge rad="0"/>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="228600">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:glow>
+              <a:softEdge rad="0"/>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PIVOT!$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:alpha val="84000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="228600">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:glow>
+              <a:softEdge rad="0"/>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="228600">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="175000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:softEdge rad="0"/>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="stdErr"/>
+            <c:noEndCap val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:f>PIVOT!$A$21:$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16/05/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PIVOT!$B$21:$B$25</c:f>
+              <c:numCache>
+                <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>180656</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>309654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-620C-4081-91B1-C08AD79DDA2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:upDownBars>
+          <c:gapWidth val="315"/>
+          <c:upBars>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:upBars>
+          <c:downBars>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:downBars>
+        </c:upDownBars>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="199646304"/>
+        <c:axId val="199652128"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="199646304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="199652128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="199652128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="199646304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="223">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="46000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="99000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Day"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Day"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8423275" y="209551"/>
+              <a:ext cx="1816100" cy="1790700"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>554037</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>230187</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>579437</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>738187</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>17462</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>93662</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rounded Rectangle 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1031875" y="333375"/>
+          <a:ext cx="18700750" cy="6524625"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:effectLst>
+          <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2159000" y="1092200"/>
+          <a:ext cx="2422525" cy="2038350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>460375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>281214</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>320675</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rounded Rectangle 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2090964" y="3321050"/>
+          <a:ext cx="7278461" cy="2733675"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Day 1"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Day 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2447925" y="1206500"/>
+              <a:ext cx="1797050" cy="1790700"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>101601</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>460374</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>126999</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621569560186" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="2">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-17T00:00:00" count="4">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621570833333" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Table1].[Db id].[Db id]" caption="Db id" numFmtId="0" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="4">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="4"/>
+        <n v="5"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Db id].&amp;[1]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Db id].&amp;[2]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Db id].&amp;[4]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Db id].&amp;[5]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" numFmtId="0" hierarchy="11" level="32767"/>
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="13" level="32767"/>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621572453703" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111353158"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-17T00:00:00" count="4">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="13" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.62157372685" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111353158"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-17T00:00:00" count="4">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621568518516" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1">
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
+        <x14:sourceConnection name="ThisWorkbookDataModel"/>
+      </ext>
+    </extLst>
+  </cacheSource>
+  <cacheFields count="0"/>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="9" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="208" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+  <location ref="A20:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
+      <items count="5">
+        <item x="0" e="0"/>
+        <item x="1" e="0"/>
+        <item x="2" e="0"/>
+        <item x="3" e="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Difference_Rise" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="20" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="14">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="211" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="A10:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
+      <items count="5">
+        <item x="0" e="0"/>
+        <item x="1" e="0"/>
+        <item x="2" e="0"/>
+        <item x="3" e="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Difference_Outstanding" fld="0" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="14">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="202" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+  <location ref="D10:E15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Difference_Outstanding" fld="0" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="15" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="14">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="205" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A2:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Outstanding" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Difference_Outstanding" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Difference_Rise" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="14">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="0"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Day" sourceName="[Table1].[Day]">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable3"/>
+    <pivotTable tabId="3" name="PivotTable4"/>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <olap pivotCacheId="9">
+      <levels count="2">
+        <level uniqueName="[Table1].[Day].[(All)]" sourceCaption="(All)" count="0"/>
+        <level uniqueName="[Table1].[Day].[Day]" sourceCaption="Day" count="5">
+          <ranges>
+            <range startItem="0">
+              <i n="[Table1].[Day].&amp;[2026-05-12T00:00:00]" c="12/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-13T00:00:00]" c="13/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-15T00:00:00]" c="15/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-16T00:00:00]" c="16/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-14T00:00:00]" c="14/05/2026" nd="1"/>
+            </range>
+          </ranges>
+        </level>
+      </levels>
+      <selections count="1">
+        <selection n="[Table1].[Day].[All]"/>
+      </selections>
+    </olap>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Day" cache="Slicer_Day" caption="Day" level="1" rowHeight="241300"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Day 1" cache="Slicer_Day" caption="Day" level="1" style="SlicerStyleDark5" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E2203" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:E2203"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Db id" dataDxfId="7"/>
-    <tableColumn id="22" name="Day" dataDxfId="6"/>
-    <tableColumn id="3" name="Sales product" dataDxfId="5"/>
-    <tableColumn id="2" name="Outstanding" dataDxfId="4"/>
-    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:F6"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Db id" dataDxfId="8"/>
+    <tableColumn id="22" name="Day" dataDxfId="7"/>
+    <tableColumn id="3" name="Sales product" dataDxfId="3"/>
+    <tableColumn id="2" name="Outstanding" dataDxfId="1"/>
+    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="2"/>
+    <tableColumn id="5" name="Difference_Rise" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -667,11 +8569,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ID" dataDxfId="2">
+    <tableColumn id="1" name="ID" dataDxfId="6">
       <calculatedColumnFormula>ROW()-ROW(Table1[#Headers])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Day" dataDxfId="1"/>
-    <tableColumn id="3" name="Collected" dataDxfId="0"/>
+    <tableColumn id="2" name="Day" dataDxfId="5"/>
+    <tableColumn id="3" name="Collected" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -940,15 +8842,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="29.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="29.7109375" style="1"/>
     <col min="4" max="5" width="29.7109375" style="3"/>
-    <col min="6" max="16384" width="29.7109375" style="1"/>
+    <col min="6" max="6" width="33.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="29.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -964,8 +8867,11 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>1</v>
@@ -983,8 +8889,11 @@
         <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
         <v>0</v>
       </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>2</v>
@@ -1002,8 +8911,12 @@
         <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
         <v>502833</v>
       </c>
+      <c r="F3" s="3">
+        <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E2)</f>
+        <v>502833</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>3</v>
@@ -1011,11 +8924,14 @@
       <c r="B4" s="5">
         <v>46156</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>4</v>
@@ -1023,14 +8939,49 @@
       <c r="B5" s="2">
         <v>46157</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>112353157</v>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(D3-Table1[[#This Row],[Outstanding]])</f>
+        <v>683489</v>
+      </c>
+      <c r="F5" s="3">
+        <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E3)</f>
+        <v>180656</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>ROW()-ROW(Table1[#Headers])</f>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7">
+        <v>111360014</v>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(D5-Table1[[#This Row],[Outstanding]])</f>
+        <v>993143</v>
+      </c>
+      <c r="F6" s="3">
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E5)</f>
+        <v>309654</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1106,4 +9057,263 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" customWidth="1"/>
+    <col min="5" max="5" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>113539479</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8">
+        <v>113036646</v>
+      </c>
+      <c r="C4" s="8">
+        <v>502833</v>
+      </c>
+      <c r="D4" s="8">
+        <v>502833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8">
+        <v>112353157</v>
+      </c>
+      <c r="C5" s="8">
+        <v>683489</v>
+      </c>
+      <c r="D5" s="8">
+        <v>180656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8">
+        <v>111360014</v>
+      </c>
+      <c r="C6" s="8">
+        <v>993143</v>
+      </c>
+      <c r="D6" s="8">
+        <v>309654</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8">
+        <v>450289296</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2179465</v>
+      </c>
+      <c r="D7" s="8">
+        <v>993143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>46154</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>46154</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46155</v>
+      </c>
+      <c r="B12" s="12">
+        <v>502833</v>
+      </c>
+      <c r="D12" s="11">
+        <v>46155</v>
+      </c>
+      <c r="E12" s="12">
+        <v>502833</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46157</v>
+      </c>
+      <c r="B13" s="12">
+        <v>683489</v>
+      </c>
+      <c r="D13" s="11">
+        <v>46157</v>
+      </c>
+      <c r="E13" s="12">
+        <v>683489</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46158</v>
+      </c>
+      <c r="B14" s="12">
+        <v>993143</v>
+      </c>
+      <c r="D14" s="11">
+        <v>46158</v>
+      </c>
+      <c r="E14" s="12">
+        <v>993143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="12">
+        <v>2179465</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="12">
+        <v>2179465</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>46154</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>46155</v>
+      </c>
+      <c r="B22" s="12">
+        <v>502833</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>46157</v>
+      </c>
+      <c r="B23" s="12">
+        <v>180656</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>46158</v>
+      </c>
+      <c r="B24" s="12">
+        <v>309654</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="12">
+        <v>993143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId6"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/data/Daily_Out_Standing.xlsx
+++ b/data/Daily_Out_Standing.xlsx
@@ -23,20 +23,21 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="80" r:id="rId5"/>
-    <pivotCache cacheId="83" r:id="rId6"/>
-    <pivotCache cacheId="86" r:id="rId7"/>
-    <pivotCache cacheId="89" r:id="rId8"/>
+    <pivotCache cacheId="352" r:id="rId5"/>
+    <pivotCache cacheId="355" r:id="rId6"/>
+    <pivotCache cacheId="358" r:id="rId7"/>
+    <pivotCache cacheId="361" r:id="rId8"/>
+    <pivotCache cacheId="364" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="7" r:id="rId9"/>
+        <pivotCache cacheId="274" r:id="rId10"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId10"/>
+        <x14:slicerCache r:id="rId11"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -77,15 +78,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>Db id</t>
-  </si>
-  <si>
-    <t>Sales product</t>
-  </si>
-  <si>
-    <t>MySol NEO 2</t>
   </si>
   <si>
     <t>Day</t>
@@ -120,13 +115,15 @@
   <si>
     <t>Sum of Difference_Rise</t>
   </si>
+  <si>
+    <t>(blank)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="6" formatCode="&quot;MK&quot;#,##0;[Red]\-&quot;MK&quot;#,##0"/>
+  <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
@@ -618,7 +615,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -651,19 +648,13 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -711,15 +702,130 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="49">
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="8" formatCode="#,##0.00;[Red]\-#,##0.00"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -874,7 +980,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -1266,7 +1372,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -1561,8 +1667,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable1</c:name>
-    <c:fmtId val="20"/>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable5</c:name>
+    <c:fmtId val="45"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1624,7 +1730,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PIVOT!$B$20</c:f>
+              <c:f>PIVOT!$L$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1647,7 +1753,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$21:$A$31</c:f>
+              <c:f>PIVOT!$K$23:$K$33</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -1660,7 +1766,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -1685,7 +1791,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$21:$B$31</c:f>
+              <c:f>PIVOT!$L$23:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1725,7 +1831,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-30EF-45C1-BFF0-E23B8C649049}"/>
+              <c16:uniqueId val="{00000000-F7DD-4FBE-9DCF-2EBB0E0EBBE7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1738,11 +1844,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="199646304"/>
-        <c:axId val="199652128"/>
+        <c:axId val="467483263"/>
+        <c:axId val="467481599"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="199646304"/>
+        <c:axId val="467483263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1785,7 +1891,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="199652128"/>
+        <c:crossAx val="467481599"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1793,7 +1899,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="199652128"/>
+        <c:axId val="467481599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1844,7 +1950,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="199646304"/>
+        <c:crossAx val="467483263"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2288,7 +2394,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -2832,6 +2938,23 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -2864,32 +2987,11 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2897,59 +2999,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx2">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -2966,7 +3016,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -3204,167 +3254,68 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable1</c:name>
-    <c:fmtId val="23"/>
+    <c:name>[Daily_Out_Standing.xlsx]PIVOT!PivotTable5</c:name>
+    <c:fmtId val="48"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>DIffrence Rise</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
         <c:spPr>
-          <a:ln w="34925" cap="rnd">
+          <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent5">
+                <a:satMod val="175000"/>
+                <a:alpha val="40000"/>
+              </a:schemeClr>
+            </a:glow>
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3383,12 +3334,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
+                <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3412,61 +3363,9 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="6.4007253347866916E-2"/>
-          <c:y val="4.0921432053601825E-2"/>
-          <c:w val="0.93599274665213306"/>
-          <c:h val="0.91419127483660245"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3475,7 +3374,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PIVOT!$B$20</c:f>
+              <c:f>PIVOT!$L$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3485,98 +3384,24 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent5">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:glow>
             </a:effectLst>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="6"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent1"/>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst>
-                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                    <a:srgbClr val="000000">
-                      <a:alpha val="63000"/>
-                    </a:srgbClr>
-                  </a:outerShdw>
-                </a:effectLst>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E082-425F-854F-C83C31044867}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -3592,12 +3417,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:ln>
-                      <a:noFill/>
-                    </a:ln>
+                  <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3636,9 +3461,29 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:name/>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="50800">
+                  <a:schemeClr val="accent2"/>
+                </a:glow>
+              </a:effectLst>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$21:$A$31</c:f>
+              <c:f>PIVOT!$K$23:$K$33</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -3651,7 +3496,7 @@
                   <c:v>15/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16/05/2026</c:v>
+                  <c:v>18/05/2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21/05/2026</c:v>
@@ -3676,7 +3521,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$21:$B$31</c:f>
+              <c:f>PIVOT!$L$23:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3716,7 +3561,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E082-425F-854F-C83C31044867}"/>
+              <c16:uniqueId val="{00000000-D4CD-4919-9B12-357100227A2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3729,63 +3574,24 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:upDownBars>
-          <c:gapWidth val="315"/>
-          <c:upBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="15000"/>
-                    <a:lumOff val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:upBars>
-          <c:downBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:downBars>
-        </c:upDownBars>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="199646304"/>
-        <c:axId val="199652128"/>
+        <c:axId val="467483263"/>
+        <c:axId val="467481599"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="199646304"/>
+        <c:axId val="467483263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3801,12 +3607,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3816,7 +3622,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="199652128"/>
+        <c:crossAx val="467481599"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3824,14 +3630,14 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="199652128"/>
+        <c:axId val="467481599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -3839,25 +3645,19 @@
           <a:ln>
             <a:noFill/>
           </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="50800" dist="50800" dir="5400000" sx="1000" sy="1000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="43137"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3867,26 +3667,56 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="199646304"/>
+        <c:crossAx val="467483263"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="25400">
+        <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:noFill/>
       <a:round/>
@@ -3898,14 +3728,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:defRPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3919,6 +3742,8 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -6757,7 +6582,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6768,7 +6593,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -6781,7 +6606,7 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
@@ -6798,7 +6623,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -6814,7 +6639,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -6858,35 +6683,45 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="34925" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6898,29 +6733,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -7024,8 +6861,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -7115,20 +6958,20 @@
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -7141,17 +6984,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -7183,7 +7015,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -7192,13 +7024,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -7252,98 +7085,32 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Day"/>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Day"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8423275" y="209551"/>
-              <a:ext cx="1816100" cy="1790700"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>71437</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>411162</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7394,20 +7161,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>515937</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>174625</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>277812</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvPr id="6" name="Chart 5"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -7422,6 +7189,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Day"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Day"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11572875" y="523875"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7431,8 +7270,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>253998</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>52</xdr:col>
@@ -7447,14 +7286,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="253998" y="1381125"/>
-          <a:ext cx="31940501" cy="10501312"/>
+          <a:off x="253998" y="952500"/>
+          <a:ext cx="31940501" cy="10929937"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:sysClr val="window" lastClr="FFFFFF"/>
+          <a:schemeClr val="bg1"/>
         </a:solidFill>
         <a:ln cap="flat"/>
         <a:effectLst>
@@ -7486,7 +7325,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7494,14 +7337,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>476251</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>9074</xdr:rowOff>
     </xdr:to>
@@ -7512,8 +7355,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1285875" y="2095500"/>
-          <a:ext cx="2476500" cy="4009574"/>
+          <a:off x="619125" y="2095500"/>
+          <a:ext cx="3571876" cy="4009574"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7569,16 +7412,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>476251</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>523876</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7601,8 +7444,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -7619,8 +7462,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1238249" y="6477000"/>
-          <a:ext cx="11739564" cy="4786313"/>
+          <a:off x="619125" y="6477000"/>
+          <a:ext cx="12358688" cy="4786313"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7661,24 +7504,88 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>261937</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:rowOff>19500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>384562</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="Day 1"/>
+            <xdr:cNvPr id="10" name="Day 1"/>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -7702,8 +7609,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1500187" y="2405063"/>
-              <a:ext cx="1980000" cy="3429000"/>
+              <a:off x="809625" y="2305500"/>
+              <a:ext cx="3095625" cy="3600000"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7733,79 +7640,259 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465531712965" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.52696354167" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="4">
+    <cacheField name="[Table1].[Db id].[Db id]" caption="Db id" numFmtId="0" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12" count="10">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="6"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Db id].&amp;[1]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Db id].&amp;[2]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Db id].&amp;[3]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Db id].&amp;[4]"/>
+            <x15:cachedUniqueName index="4" name="[Table1].[Db id].&amp;[6]"/>
+            <x15:cachedUniqueName index="5" name="[Table1].[Db id].&amp;[8]"/>
+            <x15:cachedUniqueName index="6" name="[Table1].[Db id].&amp;[9]"/>
+            <x15:cachedUniqueName index="7" name="[Table1].[Db id].&amp;[10]"/>
+            <x15:cachedUniqueName index="8" name="[Table1].[Db id].&amp;[11]"/>
+            <x15:cachedUniqueName index="9" name="[Table1].[Db id].&amp;[12]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" numFmtId="0" hierarchy="9" level="32767"/>
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="10" level="32767"/>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="13">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.52696412037" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="2">
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="2" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111353158"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="11">
+        <m/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-18T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-24T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="13">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.526964467594" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="10" level="32767"/>
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="2" level="1">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="7">
         <n v="113539479"/>
         <n v="113036646"/>
@@ -7834,7 +7921,7 @@
         <d v="2026-05-12T00:00:00"/>
         <d v="2026-05-13T00:00:00"/>
         <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
+        <d v="2026-05-18T00:00:00"/>
         <d v="2026-05-21T00:00:00"/>
         <d v="2026-05-24T00:00:00"/>
         <d v="2026-05-26T00:00:00"/>
@@ -7844,7 +7931,7 @@
       </sharedItems>
     </cacheField>
   </cacheFields>
-  <cacheHierarchies count="14">
+  <cacheHierarchies count="13">
     <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
       <fieldsUsage count="2">
@@ -7852,7 +7939,6 @@
         <fieldUsage x="2"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
@@ -7877,17 +7963,10 @@
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -7897,103 +7976,11 @@
       </fieldsUsage>
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532175927" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-13T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
-        <d v="2026-05-21T00:00:00"/>
-        <d v="2026-05-24T00:00:00"/>
-        <d v="2026-05-26T00:00:00"/>
-        <d v="2026-05-27T00:00:00"/>
-        <d v="2026-05-28T00:00:00"/>
-        <d v="2026-05-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="4"/>
@@ -8003,138 +7990,7 @@
     <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532523151" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Table1].[Db id].[Db id]" caption="Db id" numFmtId="0" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12" count="10">
-        <n v="1"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="6"/>
-        <n v="8"/>
-        <n v="9"/>
-        <n v="10"/>
-        <n v="11"/>
-        <n v="12"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Table1].[Db id].&amp;[1]"/>
-            <x15:cachedUniqueName index="1" name="[Table1].[Db id].&amp;[2]"/>
-            <x15:cachedUniqueName index="2" name="[Table1].[Db id].&amp;[4]"/>
-            <x15:cachedUniqueName index="3" name="[Table1].[Db id].&amp;[5]"/>
-            <x15:cachedUniqueName index="4" name="[Table1].[Db id].&amp;[6]"/>
-            <x15:cachedUniqueName index="5" name="[Table1].[Db id].&amp;[8]"/>
-            <x15:cachedUniqueName index="6" name="[Table1].[Db id].&amp;[9]"/>
-            <x15:cachedUniqueName index="7" name="[Table1].[Db id].&amp;[10]"/>
-            <x15:cachedUniqueName index="8" name="[Table1].[Db id].&amp;[11]"/>
-            <x15:cachedUniqueName index="9" name="[Table1].[Db id].&amp;[12]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
-    <cacheField name="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" numFmtId="0" hierarchy="11" level="32767"/>
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="13" level="32767"/>
-    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="3"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -8159,33 +8015,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532986113" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.526964814817" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
-        <n v="113539479"/>
-        <n v="113036646"/>
-        <n v="112353157"/>
-        <n v="111353158"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
-            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
-            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
-            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
+  <cacheFields count="2">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="10" level="32767"/>
     <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
         <d v="2026-05-12T00:00:00"/>
         <d v="2026-05-13T00:00:00"/>
         <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
+        <d v="2026-05-18T00:00:00"/>
         <d v="2026-05-21T00:00:00"/>
         <d v="2026-05-24T00:00:00"/>
         <d v="2026-05-26T00:00:00"/>
@@ -8194,9 +8033,8 @@
         <d v="2026-05-30T00:00:00"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="13" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="14">
+  <cacheHierarchies count="13">
     <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
       <fieldsUsage count="2">
@@ -8204,13 +8042,7 @@
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
@@ -8229,34 +8061,34 @@
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="2"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="4"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
+          <x15:cacheHierarchy aggregatedColumn="4"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -8281,19 +8113,33 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.462236226849" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1">
-    <extLst>
-      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
-        <x14:sourceConnection name="ThisWorkbookDataModel"/>
-      </ext>
-    </extLst>
-  </cacheSource>
-  <cacheFields count="0"/>
-  <cacheHierarchies count="14">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.52696516204" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="2">
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-18T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-24T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="12" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="13">
     <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
@@ -8313,21 +8159,104 @@
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="2"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.52491226852" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1">
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
+        <x14:sourceConnection name="ThisWorkbookDataModel"/>
+      </ext>
+    </extLst>
+  </cacheSource>
+  <cacheFields count="0"/>
+  <cacheHierarchies count="13">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Difference_Rise]" caption="Count of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="4"/>
@@ -8337,7 +8266,7 @@
     <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
+          <x15:cacheHierarchy aggregatedColumn="4"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -8345,44 +8274,34 @@
   <kpis count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="11" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="18" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="A20:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="364" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="49">
+  <location ref="K22:L33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="5">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
-      <items count="11">
-        <item x="0" e="0"/>
-        <item x="1" e="0"/>
-        <item x="2" e="0"/>
-        <item x="3" e="0"/>
-        <item x="4" e="0"/>
-        <item x="5" e="0"/>
-        <item x="6" e="0"/>
-        <item x="7" e="0"/>
-        <item x="8" e="0"/>
-        <item x="9" e="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
+  <rowFields count="1">
     <field x="0"/>
   </rowFields>
   <rowItems count="11">
@@ -8424,10 +8343,21 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Difference_Rise" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
+    <dataField name="Sum of Difference_Rise" fld="1" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="20" format="0" series="1">
+  <formats count="3">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="45" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8436,16 +8366,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="21" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="2" series="1">
+    <chartFormat chart="48" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8455,10 +8376,113 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="14">
+  <pivotHierarchies count="13">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="355" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A20:A32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
+      <items count="12">
+        <item x="0" e="0"/>
+        <item x="1" e="0"/>
+        <item x="2" e="0"/>
+        <item x="3" e="0"/>
+        <item x="4" e="0"/>
+        <item x="5" e="0"/>
+        <item x="6" e="0"/>
+        <item x="7" e="0"/>
+        <item x="8" e="0"/>
+        <item x="9" e="0"/>
+        <item x="10" e="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <pivotHierarchies count="13">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -8474,7 +8498,7 @@
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="2">
     <rowHierarchyUsage hierarchyUsage="1"/>
-    <rowHierarchyUsage hierarchyUsage="3"/>
+    <rowHierarchyUsage hierarchyUsage="2"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -8489,8 +8513,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="83" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="361" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
   <location ref="D21:E32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -8583,10 +8607,9 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="14">
+  <pivotHierarchies count="13">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -8616,10 +8639,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="86" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="A2:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="352" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A2:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
       <items count="11">
         <item x="0"/>
@@ -8635,7 +8658,6 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1"/>
@@ -8681,26 +8703,21 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="2">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
   </colItems>
-  <dataFields count="3">
+  <dataFields count="2">
     <dataField name="Sum of Outstanding" fld="1" baseField="0" baseItem="0"/>
     <dataField name="Sum of Difference_Outstanding" fld="2" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Difference_Rise" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotHierarchies count="14">
+  <pivotHierarchies count="13">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -8733,8 +8750,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="80" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="358" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
   <location ref="A36:B47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -8811,7 +8828,7 @@
   <dataFields count="1">
     <dataField name="Sum of Difference_Outstanding" fld="0" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
-  <chartFormats count="3">
+  <chartFormats count="2">
     <chartFormat chart="13" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -8821,16 +8838,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="17" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="9" series="1">
+    <chartFormat chart="16" format="8" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8840,10 +8848,9 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="14">
+  <pivotHierarchies count="13">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -8859,7 +8866,7 @@
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="2">
     <rowHierarchyUsage hierarchyUsage="1"/>
-    <rowHierarchyUsage hierarchyUsage="3"/>
+    <rowHierarchyUsage hierarchyUsage="2"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -8877,22 +8884,23 @@
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Day" sourceName="[Table1].[Day]">
   <pivotTables>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="PivotTable1"/>
     <pivotTable tabId="3" name="PivotTable3"/>
     <pivotTable tabId="3" name="PivotTable4"/>
-    <pivotTable tabId="3" name="PivotTable2"/>
-    <pivotTable tabId="3" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable5"/>
   </pivotTables>
   <data>
-    <olap pivotCacheId="11">
+    <olap pivotCacheId="18">
       <levels count="2">
         <level uniqueName="[Table1].[Day].[(All)]" sourceCaption="(All)" count="0"/>
-        <level uniqueName="[Table1].[Day].[Day]" sourceCaption="Day" count="12">
+        <level uniqueName="[Table1].[Day].[Day]" sourceCaption="Day" count="11">
           <ranges>
             <range startItem="0">
               <i n="[Table1].[Day].&amp;[2026-05-12T00:00:00]" c="12/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-13T00:00:00]" c="13/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-15T00:00:00]" c="15/05/2026"/>
-              <i n="[Table1].[Day].&amp;[2026-05-16T00:00:00]" c="16/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-18T00:00:00]" c="18/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-21T00:00:00]" c="21/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-24T00:00:00]" c="24/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-26T00:00:00]" c="26/05/2026"/>
@@ -8900,7 +8908,6 @@
               <i n="[Table1].[Day].&amp;[2026-05-28T00:00:00]" c="28/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-30T00:00:00]" c="30/05/2026"/>
               <i n="[Table1].[Day].&amp;" c="(blank)" nd="1"/>
-              <i n="[Table1].[Day].&amp;[2026-05-14T00:00:00]" c="14/05/2026" nd="1"/>
             </range>
           </ranges>
         </level>
@@ -8921,20 +8928,23 @@
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <slicer name="Day 1" cache="Slicer_Day" caption="Day" level="1" style="SlicerStyleDark5" rowHeight="216000"/>
+  <slicer name="Day 1" cache="Slicer_Day" caption="Day" level="1" style="SlicerStyleDark5" rowHeight="504000"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="1">
-  <autoFilter ref="A1:F16"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Db id" dataDxfId="6"/>
-    <tableColumn id="22" name="Day" dataDxfId="5"/>
-    <tableColumn id="3" name="Sales product" dataDxfId="4"/>
-    <tableColumn id="2" name="Outstanding" dataDxfId="3"/>
-    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="0"/>
-    <tableColumn id="5" name="Difference_Rise" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E15" totalsRowShown="0" headerRowDxfId="48" dataDxfId="42">
+  <autoFilter ref="A1:E15"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Db id" dataDxfId="44"/>
+    <tableColumn id="22" name="Day" dataDxfId="43"/>
+    <tableColumn id="2" name="Outstanding" dataDxfId="40"/>
+    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="41">
+      <calculatedColumnFormula>SUM(C1-Table1[[#This Row],[Outstanding]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" name="Difference_Rise" dataDxfId="39">
+      <calculatedColumnFormula>SUM(Table1[[#This Row],[Difference_Outstanding]]-D1)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8944,11 +8954,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ID" dataDxfId="9">
+    <tableColumn id="1" name="ID" dataDxfId="47">
       <calculatedColumnFormula>ROW()-ROW(Table1[#Headers])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Day" dataDxfId="8"/>
-    <tableColumn id="3" name="Collected" dataDxfId="7"/>
+    <tableColumn id="2" name="Day" dataDxfId="46"/>
+    <tableColumn id="3" name="Collected" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9217,36 +9227,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="29.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="29.7109375" style="1"/>
-    <col min="4" max="5" width="29.7109375" style="3"/>
-    <col min="6" max="6" width="33.85546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="29.7109375" style="1"/>
+    <col min="1" max="2" width="29.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" style="14"/>
+    <col min="4" max="4" width="29.7109375" style="3"/>
+    <col min="5" max="5" width="33.85546875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="29.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>1</v>
@@ -9254,21 +9262,17 @@
       <c r="B2" s="10">
         <v>46154</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>2</v>
+      <c r="C2" s="15">
+        <v>113539479</v>
       </c>
       <c r="D2" s="13">
-        <v>113539479</v>
+        <v>0</v>
       </c>
       <c r="E2" s="13">
-        <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>2</v>
@@ -9276,249 +9280,198 @@
       <c r="B3" s="10">
         <v>46155</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>2</v>
+      <c r="C3" s="15">
+        <v>113036646</v>
       </c>
       <c r="D3" s="13">
-        <v>113036646</v>
+        <f>SUM(C2-Table1[[#This Row],[Outstanding]])</f>
+        <v>502833</v>
       </c>
       <c r="E3" s="13">
-        <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D2)</f>
         <v>502833</v>
       </c>
-      <c r="F3" s="13">
-        <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E2)</f>
-        <v>502833</v>
-      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>3</v>
       </c>
-      <c r="B4" s="15">
-        <v>46156</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C4" s="16">
+        <v>112353157</v>
+      </c>
+      <c r="D4" s="13">
+        <f>SUM(C3-Table1[[#This Row],[Outstanding]])</f>
+        <v>683489</v>
+      </c>
+      <c r="E4" s="13">
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D3)</f>
+        <v>180656</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>4</v>
       </c>
       <c r="B5" s="10">
-        <v>46157</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="17">
-        <v>112353157</v>
+        <v>46160</v>
+      </c>
+      <c r="C5" s="16">
+        <v>111360014</v>
+      </c>
+      <c r="D5" s="13">
+        <f>SUM(C4-Table1[[#This Row],[Outstanding]])</f>
+        <v>993143</v>
       </c>
       <c r="E5" s="13">
-        <f>SUM(D3-Table1[[#This Row],[Outstanding]])</f>
-        <v>683489</v>
-      </c>
-      <c r="F5" s="13">
-        <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E3)</f>
-        <v>180656</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D4)</f>
+        <v>309654</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <f>ROW()-ROW(Table1[#Headers])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="10">
-        <v>46158</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="17">
-        <v>111360014</v>
+        <v>46163</v>
+      </c>
+      <c r="C6" s="16">
+        <v>110262017</v>
+      </c>
+      <c r="D6" s="13">
+        <f>SUM(C5-Table1[[#This Row],[Outstanding]])</f>
+        <v>1097997</v>
       </c>
       <c r="E6" s="13">
-        <f>SUM(D5-Table1[[#This Row],[Outstanding]])</f>
-        <v>993143</v>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E5)</f>
-        <v>309654</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D5)</f>
+        <v>104854</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="10">
-        <v>46163</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17">
-        <v>110262017</v>
+        <v>46166</v>
+      </c>
+      <c r="C7" s="15">
+        <v>109501260</v>
+      </c>
+      <c r="D7" s="13">
+        <f>SUM(C6-Table1[[#This Row],[Outstanding]])</f>
+        <v>760757</v>
       </c>
       <c r="E7" s="13">
-        <f>SUM(D6-Table1[[#This Row],[Outstanding]])</f>
-        <v>1097997</v>
-      </c>
-      <c r="F7" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E6)</f>
-        <v>104854</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D6)</f>
+        <v>-337240</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="10">
-        <v>46166</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>2</v>
+        <v>46168</v>
+      </c>
+      <c r="C8" s="16">
+        <v>108785498</v>
       </c>
       <c r="D8" s="13">
-        <v>109501260</v>
+        <f>SUM(C7-Table1[[#This Row],[Outstanding]])</f>
+        <v>715762</v>
       </c>
       <c r="E8" s="13">
-        <f>SUM(D7-Table1[[#This Row],[Outstanding]])</f>
-        <v>760757</v>
-      </c>
-      <c r="F8" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E7)</f>
-        <v>-337240</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D7)</f>
+        <v>-44995</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="10">
-        <v>46168</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="17">
-        <v>108785498</v>
+        <v>46169</v>
+      </c>
+      <c r="C9" s="16">
+        <v>108388698</v>
+      </c>
+      <c r="D9" s="13">
+        <f>SUM(C8-Table1[[#This Row],[Outstanding]])</f>
+        <v>396800</v>
       </c>
       <c r="E9" s="13">
-        <f>SUM(D8-Table1[[#This Row],[Outstanding]])</f>
-        <v>715762</v>
-      </c>
-      <c r="F9" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E8)</f>
-        <v>-44995</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D8)</f>
+        <v>-318962</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="10">
-        <v>46169</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="18">
-        <v>108388698</v>
+        <v>46170</v>
+      </c>
+      <c r="C10" s="16">
+        <v>108062692</v>
+      </c>
+      <c r="D10" s="13">
+        <f>SUM(C9-Table1[[#This Row],[Outstanding]])</f>
+        <v>326006</v>
       </c>
       <c r="E10" s="13">
-        <f>SUM(D9-Table1[[#This Row],[Outstanding]])</f>
-        <v>396800</v>
-      </c>
-      <c r="F10" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E9)</f>
-        <v>-318962</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D9)</f>
+        <v>-70794</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="10">
-        <v>46170</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="18">
-        <v>108062692</v>
+        <v>46172</v>
+      </c>
+      <c r="C11" s="16">
+        <v>107438871</v>
+      </c>
+      <c r="D11" s="13">
+        <f>SUM(C10-Table1[[#This Row],[Outstanding]])</f>
+        <v>623821</v>
       </c>
       <c r="E11" s="13">
-        <f>SUM(D10-Table1[[#This Row],[Outstanding]])</f>
-        <v>326006</v>
-      </c>
-      <c r="F11" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E10)</f>
-        <v>-70794</v>
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-D10)</f>
+        <v>297815</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>12</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46172</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="18">
-        <v>107438871</v>
-      </c>
-      <c r="E12" s="13">
-        <f>SUM(D11-Table1[[#This Row],[Outstanding]])</f>
-        <v>623821</v>
-      </c>
-      <c r="F12" s="13">
-        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E11)</f>
-        <v>297815</v>
-      </c>
+    <row r="12" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="15"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+    <row r="14" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="15"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+    <row r="15" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="15"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D2:E2" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -9537,13 +9490,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9600,33 +9553,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E47"/>
+  <dimension ref="A2:L47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" customWidth="1"/>
-    <col min="4" max="4" width="31.85546875" customWidth="1"/>
+    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="12" max="12" width="31.85546875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -9636,11 +9587,8 @@
       <c r="C3" s="7">
         <v>0</v>
       </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>2</v>
       </c>
@@ -9650,13 +9598,10 @@
       <c r="C4" s="7">
         <v>502833</v>
       </c>
-      <c r="D4" s="7">
-        <v>502833</v>
-      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="7">
         <v>112353157</v>
@@ -9664,13 +9609,10 @@
       <c r="C5" s="7">
         <v>683489</v>
       </c>
-      <c r="D5" s="7">
-        <v>180656</v>
-      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7">
         <v>111360014</v>
@@ -9678,11 +9620,8 @@
       <c r="C6" s="7">
         <v>993143</v>
       </c>
-      <c r="D6" s="7">
-        <v>309654</v>
-      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -9692,11 +9631,8 @@
       <c r="C7" s="7">
         <v>1097997</v>
       </c>
-      <c r="D7" s="7">
-        <v>104854</v>
-      </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -9706,11 +9642,8 @@
       <c r="C8" s="7">
         <v>760757</v>
       </c>
-      <c r="D8" s="7">
-        <v>-337240</v>
-      </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -9720,11 +9653,8 @@
       <c r="C9" s="7">
         <v>715762</v>
       </c>
-      <c r="D9" s="7">
-        <v>-44995</v>
-      </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -9734,11 +9664,8 @@
       <c r="C10" s="7">
         <v>396800</v>
       </c>
-      <c r="D10" s="7">
-        <v>-318962</v>
-      </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -9748,11 +9675,8 @@
       <c r="C11" s="7">
         <v>326006</v>
       </c>
-      <c r="D11" s="7">
-        <v>-70794</v>
-      </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -9762,13 +9686,10 @@
       <c r="C12" s="7">
         <v>623821</v>
       </c>
-      <c r="D12" s="7">
-        <v>297815</v>
-      </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="7">
         <v>1102728332</v>
@@ -9776,38 +9697,26 @@
       <c r="C13" s="7">
         <v>6100608</v>
       </c>
-      <c r="D13" s="7">
-        <v>623821</v>
-      </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
         <v>46154</v>
-      </c>
-      <c r="B21" s="11">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
-        <v>46155</v>
-      </c>
-      <c r="B22" s="11">
-        <v>502833</v>
       </c>
       <c r="D22" s="10">
         <v>46154</v>
@@ -9815,13 +9724,16 @@
       <c r="E22" s="11">
         <v>0</v>
       </c>
+      <c r="K22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>46157</v>
-      </c>
-      <c r="B23" s="11">
-        <v>180656</v>
+        <v>46155</v>
       </c>
       <c r="D23" s="10">
         <v>46155</v>
@@ -9829,13 +9741,16 @@
       <c r="E23" s="11">
         <v>502833</v>
       </c>
+      <c r="K23" s="10">
+        <v>46154</v>
+      </c>
+      <c r="L23" s="11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>46158</v>
-      </c>
-      <c r="B24" s="11">
-        <v>309654</v>
+        <v>46157</v>
       </c>
       <c r="D24" s="10">
         <v>46157</v>
@@ -9843,27 +9758,33 @@
       <c r="E24" s="11">
         <v>683489</v>
       </c>
+      <c r="K24" s="10">
+        <v>46155</v>
+      </c>
+      <c r="L24" s="11">
+        <v>502833</v>
+      </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
-        <v>46163</v>
-      </c>
-      <c r="B25" s="11">
-        <v>104854</v>
+        <v>46160</v>
       </c>
       <c r="D25" s="10">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="E25" s="11">
         <v>993143</v>
       </c>
+      <c r="K25" s="10">
+        <v>46157</v>
+      </c>
+      <c r="L25" s="11">
+        <v>180656</v>
+      </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
-        <v>46166</v>
-      </c>
-      <c r="B26" s="11">
-        <v>-337240</v>
+        <v>46163</v>
       </c>
       <c r="D26" s="10">
         <v>46163</v>
@@ -9871,13 +9792,16 @@
       <c r="E26" s="11">
         <v>1097997</v>
       </c>
+      <c r="K26" s="10">
+        <v>46160</v>
+      </c>
+      <c r="L26" s="11">
+        <v>309654</v>
+      </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
-        <v>46168</v>
-      </c>
-      <c r="B27" s="11">
-        <v>-44995</v>
+        <v>46166</v>
       </c>
       <c r="D27" s="10">
         <v>46166</v>
@@ -9885,13 +9809,16 @@
       <c r="E27" s="11">
         <v>760757</v>
       </c>
+      <c r="K27" s="10">
+        <v>46163</v>
+      </c>
+      <c r="L27" s="11">
+        <v>104854</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
-        <v>46169</v>
-      </c>
-      <c r="B28" s="11">
-        <v>-318962</v>
+        <v>46168</v>
       </c>
       <c r="D28" s="10">
         <v>46168</v>
@@ -9899,13 +9826,16 @@
       <c r="E28" s="11">
         <v>715762</v>
       </c>
+      <c r="K28" s="10">
+        <v>46166</v>
+      </c>
+      <c r="L28" s="11">
+        <v>-337240</v>
+      </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
-        <v>46170</v>
-      </c>
-      <c r="B29" s="11">
-        <v>-70794</v>
+        <v>46169</v>
       </c>
       <c r="D29" s="10">
         <v>46169</v>
@@ -9913,13 +9843,16 @@
       <c r="E29" s="11">
         <v>396800</v>
       </c>
+      <c r="K29" s="10">
+        <v>46168</v>
+      </c>
+      <c r="L29" s="11">
+        <v>-44995</v>
+      </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
-        <v>46172</v>
-      </c>
-      <c r="B30" s="11">
-        <v>297815</v>
+        <v>46170</v>
       </c>
       <c r="D30" s="10">
         <v>46170</v>
@@ -9927,13 +9860,16 @@
       <c r="E30" s="11">
         <v>326006</v>
       </c>
+      <c r="K30" s="10">
+        <v>46169</v>
+      </c>
+      <c r="L30" s="11">
+        <v>-318962</v>
+      </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="11">
-        <v>623821</v>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>46172</v>
       </c>
       <c r="D31" s="10">
         <v>46172</v>
@@ -9941,24 +9877,47 @@
       <c r="E31" s="11">
         <v>623821</v>
       </c>
+      <c r="K31" s="10">
+        <v>46170</v>
+      </c>
+      <c r="L31" s="11">
+        <v>-70794</v>
+      </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="D32" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" s="11">
         <v>6100608</v>
       </c>
+      <c r="K32" s="10">
+        <v>46172</v>
+      </c>
+      <c r="L32" s="11">
+        <v>297815</v>
+      </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L33" s="11">
+        <v>623821</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>46154</v>
       </c>
@@ -9966,7 +9925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>46155</v>
       </c>
@@ -9974,7 +9933,7 @@
         <v>502833</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>46157</v>
       </c>
@@ -9982,15 +9941,15 @@
         <v>683489</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B40" s="11">
         <v>993143</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>46163</v>
       </c>
@@ -9998,7 +9957,7 @@
         <v>1097997</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>46166</v>
       </c>
@@ -10006,7 +9965,7 @@
         <v>760757</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -10014,7 +9973,7 @@
         <v>715762</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>46169</v>
       </c>
@@ -10022,7 +9981,7 @@
         <v>396800</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>46170</v>
       </c>
@@ -10030,7 +9989,7 @@
         <v>326006</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>46172</v>
       </c>
@@ -10038,9 +9997,9 @@
         <v>623821</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B47" s="11">
         <v>6100608</v>
@@ -10048,11 +10007,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <drawing r:id="rId7"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId6"/>
+        <x14:slicer r:id="rId8"/>
       </x14:slicerList>
     </ext>
   </extLst>
